--- a/Versão5/BRMG/Ontologia_Brasil_MG.xlsx
+++ b/Versão5/BRMG/Ontologia_Brasil_MG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BRMG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6980CA-589B-42F1-9FCA-40EDFCFF1D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB1B7F0-7F9E-43BE-8B97-366C26355E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="587" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="587" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -5112,81 +5112,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="77">
+  <dxfs count="69">
     <dxf>
       <font>
         <b val="0"/>
         <i/>
         <color theme="2" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -6162,15 +6094,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="41.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="76" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="6"/>
+    <col min="1" max="1" width="9.69140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="41.53515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="76" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -6181,7 +6113,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>45</v>
       </c>
@@ -6192,7 +6124,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
@@ -6203,7 +6135,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -6214,7 +6146,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
@@ -6226,7 +6158,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>39</v>
       </c>
@@ -6238,7 +6170,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
@@ -6249,7 +6181,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>41</v>
       </c>
@@ -6260,7 +6192,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>49</v>
       </c>
@@ -6271,7 +6203,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>51</v>
       </c>
@@ -6282,7 +6214,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>42</v>
       </c>
@@ -6293,7 +6225,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>43</v>
       </c>
@@ -6304,7 +6236,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>52</v>
       </c>
@@ -6315,7 +6247,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
@@ -6326,7 +6258,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>54</v>
       </c>
@@ -6337,7 +6269,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
         <v>55</v>
       </c>
@@ -6348,7 +6280,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
@@ -6359,19 +6291,19 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B18" s="11">
         <f ca="1">NOW()</f>
-        <v>46204.603258101852</v>
+        <v>46214.346286342596</v>
       </c>
       <c r="C18" s="75" t="s">
         <v>1326</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
         <v>1334</v>
       </c>
@@ -6382,7 +6314,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
         <v>1336</v>
       </c>
@@ -6394,7 +6326,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
         <v>1337</v>
       </c>
@@ -6406,7 +6338,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
         <v>57</v>
       </c>
@@ -6417,7 +6349,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
         <v>58</v>
       </c>
@@ -6428,7 +6360,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>59</v>
       </c>
@@ -6439,7 +6371,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>60</v>
       </c>
@@ -6450,7 +6382,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
         <v>1324</v>
       </c>
@@ -6470,38 +6402,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <dimension ref="A1:AA393"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5703125" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" style="28" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" customWidth="1"/>
-    <col min="13" max="13" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" customWidth="1"/>
+    <col min="2" max="2" width="4.69140625" customWidth="1"/>
+    <col min="3" max="3" width="9.3828125" customWidth="1"/>
+    <col min="4" max="4" width="6.69140625" customWidth="1"/>
+    <col min="5" max="5" width="8.53515625" customWidth="1"/>
+    <col min="6" max="6" width="12.69140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.3828125" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.3046875" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.3828125" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.53515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.84375" style="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.69140625" customWidth="1"/>
+    <col min="13" max="13" width="7.53515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.15234375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="217.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="224.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.42578125" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" customWidth="1"/>
-    <col min="21" max="21" width="9.85546875" customWidth="1"/>
-    <col min="22" max="22" width="6.28515625" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="47" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" customWidth="1"/>
-    <col min="25" max="25" width="16.28515625" customWidth="1"/>
-    <col min="26" max="26" width="31.140625" style="28" customWidth="1"/>
-    <col min="27" max="27" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="217.84375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="224.53515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.3828125" customWidth="1"/>
+    <col min="20" max="20" width="8.69140625" customWidth="1"/>
+    <col min="21" max="21" width="9.84375" customWidth="1"/>
+    <col min="22" max="22" width="6.3046875" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" style="47" customWidth="1"/>
+    <col min="24" max="24" width="13.3828125" customWidth="1"/>
+    <col min="25" max="25" width="16.3046875" customWidth="1"/>
+    <col min="26" max="26" width="31.15234375" style="28" customWidth="1"/>
+    <col min="27" max="27" width="255.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -6584,7 +6516,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="31">
         <v>2</v>
       </c>
@@ -6676,7 +6608,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="31">
         <v>3</v>
       </c>
@@ -6768,7 +6700,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="31">
         <v>4</v>
       </c>
@@ -6860,7 +6792,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="31">
         <v>5</v>
       </c>
@@ -6952,7 +6884,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="31">
         <v>6</v>
       </c>
@@ -7044,7 +6976,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="31">
         <v>7</v>
       </c>
@@ -7136,7 +7068,7 @@
         <v>Cast Iron Pipe for water and sewage networks of basic sanitation.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="31">
         <v>8</v>
       </c>
@@ -7228,7 +7160,7 @@
         <v>PVC (Polyvinyl Chloride) pipe for domestic water and sewage networks.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="31">
         <v>9</v>
       </c>
@@ -7320,7 +7252,7 @@
         <v>Oriented PVC Pipe (Polyvinyl Chloride). More resistant material than normal PVC for water and sewage networks.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="31">
         <v>10</v>
       </c>
@@ -7412,7 +7344,7 @@
         <v>Brass pipe for water networks.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="31">
         <v>11</v>
       </c>
@@ -7504,7 +7436,7 @@
         <v>Copper pipe for hot water or gas networks.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="31">
         <v>12</v>
       </c>
@@ -7596,7 +7528,7 @@
         <v>HDPE (High Density Polyethylene) thermofusion tube.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="31">
         <v>13</v>
       </c>
@@ -7688,7 +7620,7 @@
         <v>Steel pipe for plumbing.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="31">
         <v>14</v>
       </c>
@@ -7782,7 +7714,7 @@
         <v>Continent.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="31">
         <v>15</v>
       </c>
@@ -7874,7 +7806,7 @@
         <v>SubContinent.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="31">
         <v>16</v>
       </c>
@@ -7966,7 +7898,7 @@
         <v>Region that defines characteristics of life in the natural environment.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="31">
         <v>17</v>
       </c>
@@ -8059,7 +7991,7 @@
         <v>Country.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="31">
         <v>18</v>
       </c>
@@ -8151,7 +8083,7 @@
         <v>Nation</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="31">
         <v>19</v>
       </c>
@@ -8244,7 +8176,7 @@
         <v>Geographic Region of Brazil. of Brazil there are 5 main Geographic Regions.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="31">
         <v>20</v>
       </c>
@@ -8337,7 +8269,7 @@
         <v>Intermediate Geographic Region. Defined by the IBGE of Brazil, there are 133 Intermediate Geographic Regions, of a larger scale, which are articulated by regional capitals or large urban centers.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="31">
         <v>21</v>
       </c>
@@ -8430,7 +8362,7 @@
         <v>Immediate geographic region. Defined by the IBGE of Brazil, there are 510 Geographic Regions of smaller scale, they are articulated by medium and small cities.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="31">
         <v>22</v>
       </c>
@@ -8523,7 +8455,7 @@
         <v>State.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="31">
         <v>23</v>
       </c>
@@ -8615,7 +8547,7 @@
         <v>Federative Unit of Brazil.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="31">
         <v>24</v>
       </c>
@@ -8708,7 +8640,7 @@
         <v>Province.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="31">
         <v>25</v>
       </c>
@@ -8801,7 +8733,7 @@
         <v>Capital.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="31">
         <v>26</v>
       </c>
@@ -8894,7 +8826,7 @@
         <v>City.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="31">
         <v>27</v>
       </c>
@@ -8987,7 +8919,7 @@
         <v>Metropolis.</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="31">
         <v>28</v>
       </c>
@@ -9080,7 +9012,7 @@
         <v>Municipality.</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="31">
         <v>29</v>
       </c>
@@ -9173,7 +9105,7 @@
         <v>Climatic region.</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="31">
         <v>30</v>
       </c>
@@ -9266,7 +9198,7 @@
         <v>Climate zone.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="31">
         <v>31</v>
       </c>
@@ -9359,7 +9291,7 @@
         <v>Local climate zone (FTZ) according to Stewart and Oke's methodology for qualifying heat islands in urban areas.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="31">
         <v>32</v>
       </c>
@@ -9451,7 +9383,7 @@
         <v>Ifcreferent defines a position at a specific offset along an alignment curve.</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="31">
         <v>33</v>
       </c>
@@ -9543,7 +9475,7 @@
         <v>Represents where an administrative (city or state) or maintenance boundary (different companies or regionals) intersects the linear element (rails or roads) being measured.</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="31">
         <v>34</v>
       </c>
@@ -9635,7 +9567,7 @@
         <v>It is the location of an intersection specified by the name of the referent. the intersection location of the intersection's street reference lines. it is not precise or deterministic.</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="31">
         <v>35</v>
       </c>
@@ -9727,7 +9659,7 @@
         <v>Used to completely describe a linearly referenced location, given by the line element.</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="31">
         <v>36</v>
       </c>
@@ -9819,7 +9751,7 @@
         <v>Point in kilometer.</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="31">
         <v>37</v>
       </c>
@@ -9911,7 +9843,7 @@
         <v>The reference is the location of a visible physical reference point in the field.</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="31">
         <v>38</v>
       </c>
@@ -10003,7 +9935,7 @@
         <v>Point in mile.</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="31">
         <v>39</v>
       </c>
@@ -10095,7 +10027,7 @@
         <v>A reference marker is a notation referent, located in the right-of-way of a highway, railroad or other transportation system spaced at uniform distances.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="31">
         <v>40</v>
       </c>
@@ -10187,7 +10119,7 @@
         <v>Season.</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="31">
         <v>41</v>
       </c>
@@ -10279,7 +10211,7 @@
         <v>Specifies the superelevation (transverse slope) at a specific location along a road alignment, and the type of transition from the previous location.</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="31">
         <v>42</v>
       </c>
@@ -10371,7 +10303,7 @@
         <v>Event type that specifies the width at a specific location along a road alignment.</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="31">
         <v>43</v>
       </c>
@@ -10463,7 +10395,7 @@
         <v>Elevation points positioned inside the land.</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="31">
         <v>44</v>
       </c>
@@ -10555,7 +10487,7 @@
         <v>Altimetric elevation points positioned on the perimeter of the land.</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="31">
         <v>45</v>
       </c>
@@ -10647,7 +10579,7 @@
         <v>Three-dimensional solid terrain. Revit models above 2024 use solid terrain models, while still maintaining the terrain mesh scheme.</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="31">
         <v>46</v>
       </c>
@@ -10739,7 +10671,7 @@
         <v>Three-dimensional maha of the terrain. Revit models prior to 2024 use surface terrain models.</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="31">
         <v>47</v>
       </c>
@@ -10831,7 +10763,7 @@
         <v>Three-dimensional terrain solid: core layer.</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="31">
         <v>48</v>
       </c>
@@ -10923,7 +10855,7 @@
         <v>Three-dimensional solid of the terrain: substrate layer.</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="31">
         <v>49</v>
       </c>
@@ -11015,7 +10947,7 @@
         <v>Three-dimensional solid of the terrain: membrane layer.</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="31">
         <v>50</v>
       </c>
@@ -11107,7 +11039,7 @@
         <v>Three-dimensional solid terrain: insulation layer.</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="31">
         <v>51</v>
       </c>
@@ -11199,7 +11131,7 @@
         <v>Three-dimensional solid of the terrain: surface layer.</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="31">
         <v>52</v>
       </c>
@@ -11291,7 +11223,7 @@
         <v>10-meter level curve.</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="31">
         <v>53</v>
       </c>
@@ -11383,7 +11315,7 @@
         <v>5 meter level curve.</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="31">
         <v>54</v>
       </c>
@@ -11475,7 +11407,7 @@
         <v>Level curve of 1 meter.</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="31">
         <v>55</v>
       </c>
@@ -11567,7 +11499,7 @@
         <v>Submetric contour line, its value must be less than 1m and can be 5 cm, 10 cm, 25 cm, etc. For adjustments of boxes or poles on the ground.</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="31">
         <v>56</v>
       </c>
@@ -11659,7 +11591,7 @@
         <v>Land polling point.</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="31">
         <v>57</v>
       </c>
@@ -11754,7 +11686,7 @@
         <v>AP stands for Planning Area.</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="31">
         <v>58</v>
       </c>
@@ -11848,7 +11780,7 @@
         <v>RA stands for Administrative Region.</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="31">
         <v>59</v>
       </c>
@@ -11940,7 +11872,7 @@
         <v>Area of Special Interest.</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="31">
         <v>60</v>
       </c>
@@ -12032,7 +11964,7 @@
         <v>Area with occupancy restrictions</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="31">
         <v>61</v>
       </c>
@@ -12124,7 +12056,7 @@
         <v>Areas of the city of Rio de Janeiro.</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="31">
         <v>62</v>
       </c>
@@ -12216,7 +12148,7 @@
         <v>City Neighborhood</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="31">
         <v>63</v>
       </c>
@@ -12308,7 +12240,7 @@
         <v>Zone of use of the municipal zoning of the city of Rio de Janeiro.</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="31">
         <v>64</v>
       </c>
@@ -12400,7 +12332,7 @@
         <v>City Neighborhood</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="31">
         <v>65</v>
       </c>
@@ -12492,7 +12424,7 @@
         <v>Block of a neighborhood.</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="31">
         <v>66</v>
       </c>
@@ -12584,7 +12516,7 @@
         <v>Large land that has not yet been subdivided.</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="31">
         <v>67</v>
       </c>
@@ -12676,7 +12608,7 @@
         <v>Urban allotment.</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="31">
         <v>68</v>
       </c>
@@ -12768,7 +12700,7 @@
         <v>Urban parcel.</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="31">
         <v>69</v>
       </c>
@@ -12860,7 +12792,7 @@
         <v>Urban lot.</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="31">
         <v>70</v>
       </c>
@@ -12953,7 +12885,7 @@
         <v>Building.</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="31">
         <v>71</v>
       </c>
@@ -13046,7 +12978,7 @@
         <v>Built block.</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="31">
         <v>72</v>
       </c>
@@ -13139,7 +13071,7 @@
         <v>Building.</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="31">
         <v>73</v>
       </c>
@@ -13232,7 +13164,7 @@
         <v>Home.</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="31">
         <v>74</v>
       </c>
@@ -13325,7 +13257,7 @@
         <v>Social Interest Housing.</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="31">
         <v>75</v>
       </c>
@@ -13417,7 +13349,7 @@
         <v>Shed.</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="31">
         <v>76</v>
       </c>
@@ -13509,7 +13441,7 @@
         <v>Edicule.</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="31">
         <v>77</v>
       </c>
@@ -13602,7 +13534,7 @@
         <v>Unity.</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="31">
         <v>78</v>
       </c>
@@ -13694,7 +13626,7 @@
         <v>Sector.</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="31">
         <v>79</v>
       </c>
@@ -13786,7 +13718,7 @@
         <v>Division.</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="31">
         <v>80</v>
       </c>
@@ -13878,7 +13810,7 @@
         <v>Department</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="31">
         <v>81</v>
       </c>
@@ -13970,7 +13902,7 @@
         <v>Environment.</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="31">
         <v>82</v>
       </c>
@@ -14062,7 +13994,7 @@
         <v>Apartment</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="31">
         <v>83</v>
       </c>
@@ -14154,7 +14086,7 @@
         <v>Circulation Center.</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="31">
         <v>84</v>
       </c>
@@ -14246,7 +14178,7 @@
         <v>National Hospital.</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="31">
         <v>85</v>
       </c>
@@ -14338,7 +14270,7 @@
         <v>State Hospital.</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="31">
         <v>86</v>
       </c>
@@ -14430,7 +14362,7 @@
         <v>Municipal Hospital.</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="31">
         <v>87</v>
       </c>
@@ -14522,7 +14454,7 @@
         <v>UBS Basic Health Unit. Primary and preventive health care offered by the SUS.</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="31">
         <v>88</v>
       </c>
@@ -14614,7 +14546,7 @@
         <v>UPA Emergency Health Care Unit. Urgencies and emergencies 24x7.</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="31">
         <v>89</v>
       </c>
@@ -14706,7 +14638,7 @@
         <v>Federal University.</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="31">
         <v>90</v>
       </c>
@@ -14798,7 +14730,7 @@
         <v>State University.</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="31">
         <v>91</v>
       </c>
@@ -14890,7 +14822,7 @@
         <v>State School.</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="31">
         <v>92</v>
       </c>
@@ -14982,7 +14914,7 @@
         <v>Municipal School.</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="31">
         <v>93</v>
       </c>
@@ -15074,7 +15006,7 @@
         <v>The application colleges are educational institutions linked to universities, with the mission of integrating theory and practice in the training of students and teachers.</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="31">
         <v>94</v>
       </c>
@@ -15166,7 +15098,7 @@
         <v>Military education institutions include military elementary and secondary education colleges as well as the vocational schools of the Armed Forces.</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="31">
         <v>95</v>
       </c>
@@ -15258,7 +15190,7 @@
         <v>Meteorological station managed by the National Institute of Meteorology (INMET) dependent on the Ministry of Agriculture and Livestock.</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="31">
         <v>96</v>
       </c>
@@ -15350,7 +15282,7 @@
         <v>IBGE Index - Number of inhabitants per square kilometer measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="31">
         <v>97</v>
       </c>
@@ -15442,7 +15374,7 @@
         <v>IBGE Index - Number of inhabitants per square kilometer measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="31">
         <v>98</v>
       </c>
@@ -15534,7 +15466,7 @@
         <v>IBGE Index - IDU (Urban Development Index) evaluates the quality of life and access to urban services measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="31">
         <v>99</v>
       </c>
@@ -15626,7 +15558,7 @@
         <v>IBGE Index - Proportion between urban and rural population measured by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="31">
         <v>100</v>
       </c>
@@ -15718,7 +15650,7 @@
         <v>IBGE Index - Measure of physical growth of cities established by the Brazilian Institute of Geography and Statistics.</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="31">
         <v>101</v>
       </c>
@@ -15810,7 +15742,7 @@
         <v>A heavy rail vehicle that pulls or pushes railway cars. They can be electric, diesel-electric or steam.</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="31">
         <v>102</v>
       </c>
@@ -15902,7 +15834,7 @@
         <v>Heavy vehicle to run on rails to transport goods (grains, ores, fuels, containers).</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="31">
         <v>103</v>
       </c>
@@ -15994,7 +15926,7 @@
         <v>Heavy vehicles to run on rails to transport people, can be equipped with toilets and special facilities.</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="31">
         <v>104</v>
       </c>
@@ -16086,7 +16018,7 @@
         <v>Heavy rail vehicle to transport people prepared with sleeping facilities.</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="31">
         <v>105</v>
       </c>
@@ -16178,7 +16110,7 @@
         <v>Heavy vehicle to run on rails to transport people in urban environments.</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="31">
         <v>106</v>
       </c>
@@ -16270,7 +16202,7 @@
         <v>Heavy vehicle to run on rails to transport people in urban environments.</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="31">
         <v>107</v>
       </c>
@@ -16362,7 +16294,7 @@
         <v>Light Rail Vehicle (VLT). System of articulated and bidirectional wagons to transport people at the level of urban surroundings.</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="31">
         <v>108</v>
       </c>
@@ -16454,7 +16386,7 @@
         <v>Bullet or high-speed train. It travels at speeds that can reach 300 km/h.</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="31">
         <v>109</v>
       </c>
@@ -16546,7 +16478,7 @@
         <v>Bullet or high-speed train. It travels at speeds that can reach 300 km/h.</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="31">
         <v>110</v>
       </c>
@@ -16638,7 +16570,7 @@
         <v>Magnetic or Maglev levitation train. It travels on a line elevated over the ground that is propelled by the attractive and repulsive forces of magnetism using superconductors.</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="31">
         <v>111</v>
       </c>
@@ -16730,7 +16662,7 @@
         <v>Tractor-type construction vehicle.</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="31">
         <v>112</v>
       </c>
@@ -16822,7 +16754,7 @@
         <v>Hydraulic excavator type construction vehicle.</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="31">
         <v>113</v>
       </c>
@@ -16914,7 +16846,7 @@
         <v>Backhoe type work vehicle.</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="31">
         <v>114</v>
       </c>
@@ -17006,7 +16938,7 @@
         <v>Motor grader-type work vehicle.</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="31">
         <v>115</v>
       </c>
@@ -17098,7 +17030,7 @@
         <v>Forklift type construction vehicle for handling and stacking pallets.</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="31">
         <v>116</v>
       </c>
@@ -17190,7 +17122,7 @@
         <v>Truck-type construction vehicle with built-in crane.</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="31">
         <v>117</v>
       </c>
@@ -17282,7 +17214,7 @@
         <v>Truck-type construction vehicle with telescopic lifting system with built-in horizontal and vertical reach.</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="31">
         <v>118</v>
       </c>
@@ -17374,7 +17306,7 @@
         <v>Crane-type operation structure moved on rails.</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="31">
         <v>119</v>
       </c>
@@ -17466,7 +17398,7 @@
         <v>High tower crane type operation structure which can operate by rotation and travel.</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="31">
         <v>120</v>
       </c>
@@ -17558,7 +17490,7 @@
         <v>Small crane type operation structure that can operate by rotation and travel.</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="31">
         <v>121</v>
       </c>
@@ -17650,7 +17582,7 @@
         <v>Crane-type operation structure in gantry format.</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="31">
         <v>122</v>
       </c>
@@ -17742,7 +17674,7 @@
         <v>High-capacity product loading vehicle with closed body.</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="31">
         <v>123</v>
       </c>
@@ -17834,7 +17766,7 @@
         <v>Cargo vehicle with a high capacity to transport fluids or fuels.</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="31">
         <v>124</v>
       </c>
@@ -17926,7 +17858,7 @@
         <v>Cargo vehicle with high capacity for transporting and unloading bulk materials such as sand, gravel, earth, rubble or gravel. The bucket can be tipped.</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="31">
         <v>125</v>
       </c>
@@ -18018,7 +17950,7 @@
         <v>High-capacity cargo vehicle with two trailers (or semi-trailers) attached to the tractor truck.</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="31">
         <v>126</v>
       </c>
@@ -18110,7 +18042,7 @@
         <v>Cargo vehicle with an open or semi-open structure at the rear.</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="31">
         <v>127</v>
       </c>
@@ -18202,7 +18134,7 @@
         <v>Cargo vehicle used to transport grains.</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="31">
         <v>128</v>
       </c>
@@ -18294,7 +18226,7 @@
         <v>Cargo vehicle used to transport cargo that needs to be kept at controlled temperatures. Essential to ensure the cold chain.</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="31">
         <v>129</v>
       </c>
@@ -18386,7 +18318,7 @@
         <v>Vehicle with cabin and engine to pull semi-trailers forming an articulated set.</v>
       </c>
     </row>
-    <row r="130" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="31">
         <v>130</v>
       </c>
@@ -18478,7 +18410,7 @@
         <v>Public transport vehicle with more than 20 passengers.</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="31">
         <v>131</v>
       </c>
@@ -18570,7 +18502,7 @@
         <v>Bus Rapid Transit (BRT) system public transport vehicle. High capacity urban bus system that operates on exclusive rails.</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="31">
         <v>132</v>
       </c>
@@ -18662,7 +18594,7 @@
         <v>Public transport vehicle with up to 20 passengers.</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="31">
         <v>133</v>
       </c>
@@ -18754,7 +18686,7 @@
         <v>Non-motorized vehicle coupled to another.</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="31">
         <v>134</v>
       </c>
@@ -18846,7 +18778,7 @@
         <v>Non-motorized vehicle coupled to another.</v>
       </c>
     </row>
-    <row r="135" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="31">
         <v>135</v>
       </c>
@@ -18938,7 +18870,7 @@
         <v>Vehicle that transports cargo and passengers simultaneously.</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="31">
         <v>136</v>
       </c>
@@ -19030,7 +18962,7 @@
         <v>Vehicles adapted for specific functions such as ambulance, fire engine, school transport, etc.</v>
       </c>
     </row>
-    <row r="137" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="31">
         <v>137</v>
       </c>
@@ -19122,7 +19054,7 @@
         <v>With a total gross weight (GVW) of up to 3,500 kg, they are classified as light. Similar to the car, but with a cargo compartment.</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="31">
         <v>138</v>
       </c>
@@ -19214,7 +19146,7 @@
         <v>With a total gross weight (GVW) of up to 3,500 kg, they are classified as light. Mixed vehicle with cabin and bucket.</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="31">
         <v>139</v>
       </c>
@@ -19306,7 +19238,7 @@
         <v>With a total gross weight (GVW) of up to 3,500 kg, they are classified as light.  Light vehicle for transporting up to 5 passengers.</v>
       </c>
     </row>
-    <row r="140" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="31">
         <v>140</v>
       </c>
@@ -19398,7 +19330,7 @@
         <v>Open, motorized two-wheeled vehicle.</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="31">
         <v>141</v>
       </c>
@@ -19490,7 +19422,7 @@
         <v>Open, motorized two-wheeled vehicle.</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="31">
         <v>142</v>
       </c>
@@ -19582,7 +19514,7 @@
         <v>Open, motorized four-wheeled vehicle.</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="31">
         <v>143</v>
       </c>
@@ -19674,7 +19606,7 @@
         <v>Open, motorized three-wheeled vehicle.</v>
       </c>
     </row>
-    <row r="144" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="31">
         <v>144</v>
       </c>
@@ -19766,7 +19698,7 @@
         <v>An open vehicle with two aligned wheels, moved by the user's own effort by means of pedals.</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="31">
         <v>145</v>
       </c>
@@ -19858,7 +19790,7 @@
         <v>Crude oil cargo ship.</v>
       </c>
     </row>
-    <row r="146" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="31">
         <v>146</v>
       </c>
@@ -19950,7 +19882,7 @@
         <v>General dry cargo ship.</v>
       </c>
     </row>
-    <row r="147" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="31">
         <v>147</v>
       </c>
@@ -20042,7 +19974,7 @@
         <v>General dry cargo ships such as grain, cement and steel, access small ports with limited infrastructure.</v>
       </c>
     </row>
-    <row r="148" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="31">
         <v>148</v>
       </c>
@@ -20134,7 +20066,7 @@
         <v>Ship of varied cargoes, equipped with its own cranes, ideal for smaller ports.</v>
       </c>
     </row>
-    <row r="149" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="31">
         <v>149</v>
       </c>
@@ -20226,7 +20158,7 @@
         <v>Dry cargo ship like coal and fertilizer, similar to the Handymax but with higher capacity.</v>
       </c>
     </row>
-    <row r="150" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="31">
         <v>150</v>
       </c>
@@ -20318,7 +20250,7 @@
         <v>Grain, coal and oil cargo ship, designed to transit the Panama Canal.</v>
       </c>
     </row>
-    <row r="151" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="31">
         <v>151</v>
       </c>
@@ -20410,7 +20342,7 @@
         <v>General cargo ship and containers. Adapted to the new locks of the Panama Canal.</v>
       </c>
     </row>
-    <row r="152" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="31">
         <v>152</v>
       </c>
@@ -20502,7 +20434,7 @@
         <v>Crude oil cargo ship, medium-sized for short and medium routes.</v>
       </c>
     </row>
-    <row r="153" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="31">
         <v>153</v>
       </c>
@@ -20594,7 +20526,7 @@
         <v>Crude oil cargo ship, designed for the Suez Canal.</v>
       </c>
     </row>
-    <row r="154" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="31">
         <v>154</v>
       </c>
@@ -20686,7 +20618,7 @@
         <v>Cargo ship iron ore and coal by routes via Cape of Good Hope or Cape Horn, as they are too large for the Suez and Panama Canals.</v>
       </c>
     </row>
-    <row r="155" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="31">
         <v>155</v>
       </c>
@@ -20778,7 +20710,7 @@
         <v>Crude oil cargo for intercontinental routes require specialized ports.</v>
       </c>
     </row>
-    <row r="156" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="31">
         <v>156</v>
       </c>
@@ -20870,7 +20802,7 @@
         <v>Supertankers used on routes between the Middle East, Asia and Europe, require dedicated terminals.</v>
       </c>
     </row>
-    <row r="157" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="31">
         <v>157</v>
       </c>
@@ -20962,7 +20894,7 @@
         <v>Iron ore cargo between Brazil and China require ports with specific infrastructure.</v>
       </c>
     </row>
-    <row r="158" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="31">
         <v>158</v>
       </c>
@@ -21054,7 +20986,7 @@
         <v>Tourist cruise ship for passengers.</v>
       </c>
     </row>
-    <row r="159" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="31">
         <v>159</v>
       </c>
@@ -21146,7 +21078,7 @@
         <v>Military ship equipped with weapons or war elements.</v>
       </c>
     </row>
-    <row r="160" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="31">
         <v>160</v>
       </c>
@@ -21238,7 +21170,7 @@
         <v>Ships with scientific functionality such as Hydrooceanographic, Oceanic or Antarctic Support vessels.</v>
       </c>
     </row>
-    <row r="161" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="31">
         <v>161</v>
       </c>
@@ -21330,7 +21262,7 @@
         <v>Sailboat designed for high speed, with a narrow hull and three high masts.</v>
       </c>
     </row>
-    <row r="162" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="31">
         <v>162</v>
       </c>
@@ -21422,7 +21354,7 @@
         <v>Support ship for entry and exit to ports.</v>
       </c>
     </row>
-    <row r="163" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="31">
         <v>163</v>
       </c>
@@ -21514,7 +21446,7 @@
         <v>Support vessel equipped with specialized systems to perform chemical and hydraulic treatments in offshore oil wells. Offshore Support Vessels (OSV).</v>
       </c>
     </row>
-    <row r="164" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="31">
         <v>164</v>
       </c>
@@ -21606,7 +21538,7 @@
         <v>High-speed vessel designed with hydrofoils to carry passengers. Usually used between neighboring cities or nearby ports. It can reach about 110 km/h (60 knots).</v>
       </c>
     </row>
-    <row r="165" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="31">
         <v>165</v>
       </c>
@@ -21698,7 +21630,7 @@
         <v>A ferry-type vessel to transport passengers usually between neighboring cities or nearby ports.</v>
       </c>
     </row>
-    <row r="166" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="31">
         <v>166</v>
       </c>
@@ -21790,7 +21722,7 @@
         <v>Boat type boat for leisure or sport.</v>
       </c>
     </row>
-    <row r="167" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="31">
         <v>167</v>
       </c>
@@ -21882,7 +21814,7 @@
         <v>Small dinghy type vessel.</v>
       </c>
     </row>
-    <row r="168" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="31">
         <v>168</v>
       </c>
@@ -21974,7 +21906,7 @@
         <v>Yacht-type vessel with full cabin structure.</v>
       </c>
     </row>
-    <row r="169" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="31">
         <v>169</v>
       </c>
@@ -22066,7 +21998,7 @@
         <v>Catamaran-type vessel with two parallel hulls.</v>
       </c>
     </row>
-    <row r="170" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="31">
         <v>170</v>
       </c>
@@ -22158,7 +22090,7 @@
         <v>Sailboat type boat for leisure or sport.</v>
       </c>
     </row>
-    <row r="171" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="31">
         <v>171</v>
       </c>
@@ -22250,7 +22182,7 @@
         <v>Airplane with two internal aisles, used on international and long-haul flights. Like Boeing or Airbus.</v>
       </c>
     </row>
-    <row r="172" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="31">
         <v>172</v>
       </c>
@@ -22342,7 +22274,7 @@
         <v>Airplane with an internal aisle, used in international and long-haul flights. Like Boeing or Airbus.</v>
       </c>
     </row>
-    <row r="173" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="31">
         <v>173</v>
       </c>
@@ -22434,7 +22366,7 @@
         <v>Learjet type executive jet.</v>
       </c>
     </row>
-    <row r="174" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="31">
         <v>174</v>
       </c>
@@ -22526,7 +22458,7 @@
         <v>Small aircraft type Cessna turboprop aircraft.</v>
       </c>
     </row>
-    <row r="175" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="31">
         <v>175</v>
       </c>
@@ -22618,7 +22550,7 @@
         <v>Small helicopter.</v>
       </c>
     </row>
-    <row r="176" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="31">
         <v>176</v>
       </c>
@@ -22710,7 +22642,7 @@
         <v>Large helicopter.</v>
       </c>
     </row>
-    <row r="177" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="31">
         <v>177</v>
       </c>
@@ -22802,7 +22734,7 @@
         <v>Drone or UAS unmanned aerial vehicle.</v>
       </c>
     </row>
-    <row r="178" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="31">
         <v>178</v>
       </c>
@@ -22894,7 +22826,7 @@
         <v>Drone or UAS unmanned aerial vehicle.</v>
       </c>
     </row>
-    <row r="179" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="31">
         <v>179</v>
       </c>
@@ -22986,7 +22918,7 @@
         <v>Drone or UAS unmanned aerial vehicle.</v>
       </c>
     </row>
-    <row r="180" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="31">
         <v>180</v>
       </c>
@@ -23078,7 +23010,7 @@
         <v>Element of urban parking: Lagoa.</v>
       </c>
     </row>
-    <row r="181" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="31">
         <v>181</v>
       </c>
@@ -23170,7 +23102,7 @@
         <v>Element of urban parking: Tree.</v>
       </c>
     </row>
-    <row r="182" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="31">
         <v>182</v>
       </c>
@@ -23262,7 +23194,7 @@
         <v>Urban parking element: Area covered by lawn.</v>
       </c>
     </row>
-    <row r="183" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="31">
         <v>183</v>
       </c>
@@ -23354,7 +23286,7 @@
         <v>Element of urban parking: Urban monument.</v>
       </c>
     </row>
-    <row r="184" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="31">
         <v>184</v>
       </c>
@@ -23446,7 +23378,7 @@
         <v>Urban parking element: Urban ornament.</v>
       </c>
     </row>
-    <row r="185" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="31">
         <v>185</v>
       </c>
@@ -23538,7 +23470,7 @@
         <v>Urban parking element: Ornamental fountain.</v>
       </c>
     </row>
-    <row r="186" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="31">
         <v>186</v>
       </c>
@@ -23630,7 +23562,7 @@
         <v>Low height pedestrian light pole.</v>
       </c>
     </row>
-    <row r="187" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="31">
         <v>187</v>
       </c>
@@ -23722,7 +23654,7 @@
         <v>Tall light poles for lighting avenues.</v>
       </c>
     </row>
-    <row r="188" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="31">
         <v>188</v>
       </c>
@@ -23814,7 +23746,7 @@
         <v>Urban traffic sign.</v>
       </c>
     </row>
-    <row r="189" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="31">
         <v>189</v>
       </c>
@@ -23906,7 +23838,7 @@
         <v>Urban information totem.</v>
       </c>
     </row>
-    <row r="190" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="31">
         <v>190</v>
       </c>
@@ -23998,7 +23930,7 @@
         <v>Intercity bus terminal station.</v>
       </c>
     </row>
-    <row r="191" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="31">
         <v>191</v>
       </c>
@@ -24090,7 +24022,7 @@
         <v>Intercity bus terminal station.</v>
       </c>
     </row>
-    <row r="192" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="31">
         <v>192</v>
       </c>
@@ -24182,7 +24114,7 @@
         <v>Bus station.</v>
       </c>
     </row>
-    <row r="193" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="31">
         <v>193</v>
       </c>
@@ -24274,7 +24206,7 @@
         <v>Urban bus stop.</v>
       </c>
     </row>
-    <row r="194" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="31">
         <v>194</v>
       </c>
@@ -24366,7 +24298,7 @@
         <v>City bus stop.</v>
       </c>
     </row>
-    <row r="195" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="31">
         <v>195</v>
       </c>
@@ -24458,7 +24390,7 @@
         <v>Local roads, generally municipal, unpaved with one lane and of modest technical standard.</v>
       </c>
     </row>
-    <row r="196" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="31">
         <v>196</v>
       </c>
@@ -24550,7 +24482,7 @@
         <v>Local roads, generally municipal, paved with one lane and of modest technical standard.</v>
       </c>
     </row>
-    <row r="197" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="31">
         <v>197</v>
       </c>
@@ -24642,7 +24574,7 @@
         <v>Paved urban roads of one lane with a width of 6 to 9 meters.</v>
       </c>
     </row>
-    <row r="198" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="31">
         <v>198</v>
       </c>
@@ -24734,7 +24666,7 @@
         <v>Paved urban roads of one lane with a width of 9 to 12 meters.</v>
       </c>
     </row>
-    <row r="199" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="31">
         <v>199</v>
       </c>
@@ -24826,7 +24758,7 @@
         <v>Paved urban roads of one or two lanes with widths of 12 to 18 meters.</v>
       </c>
     </row>
-    <row r="200" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="31">
         <v>200</v>
       </c>
@@ -24918,7 +24850,7 @@
         <v>Paved urban roads with a large flow of vehicles and public transport with a width of 20 to 30 meters.</v>
       </c>
     </row>
-    <row r="201" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="31">
         <v>201</v>
       </c>
@@ -25010,7 +24942,7 @@
         <v>High-speed urban roads with separation of lanes from 30 to 60 meters.</v>
       </c>
     </row>
-    <row r="202" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="31">
         <v>202</v>
       </c>
@@ -25102,7 +25034,7 @@
         <v>Exclusive urban road for BRT operation.</v>
       </c>
     </row>
-    <row r="203" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="31">
         <v>203</v>
       </c>
@@ -25194,7 +25126,7 @@
         <v>Lane used by vehicles.</v>
       </c>
     </row>
-    <row r="204" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="31">
         <v>204</v>
       </c>
@@ -25286,7 +25218,7 @@
         <v>Part of the public road intended for pedestrian traffic positioned next to the lanes. For the project, the Carioca Sidewalks Notebook and the NBR 9050 Standard, which deals with accessibility in urban spaces, can be consulted.</v>
       </c>
     </row>
-    <row r="205" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="31">
         <v>205</v>
       </c>
@@ -25378,7 +25310,7 @@
         <v>Lane for cyclists integrated into the lane and delimited by a lane painted on the asphalt. It is less safe than the cyclovia.</v>
       </c>
     </row>
-    <row r="206" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="31">
         <v>206</v>
       </c>
@@ -25470,7 +25402,7 @@
         <v>Exclusive lane for bicycle circulation, physically separated from the motor vehicle lanes.</v>
       </c>
     </row>
-    <row r="207" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="31">
         <v>207</v>
       </c>
@@ -25562,7 +25494,7 @@
         <v>Element that separates the road from the pedestrian sidewalk vehicles with a height of less than 35 cm.</v>
       </c>
     </row>
-    <row r="208" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="31">
         <v>208</v>
       </c>
@@ -25654,7 +25586,7 @@
         <v>ABNT standard profile, embedded in the structure, with the function of lateral protection of the road lane.</v>
       </c>
     </row>
-    <row r="209" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="31">
         <v>209</v>
       </c>
@@ -25746,7 +25678,7 @@
         <v>Element with a height of more than 1.5 m, embedded in the superstructure that works to prevent the vehicle from falling from the bridge or viaduct over subway and railway tracks.</v>
       </c>
     </row>
-    <row r="210" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="31">
         <v>210</v>
       </c>
@@ -25838,7 +25770,7 @@
         <v>Continuous or hollow element of pedestrian protection on the edge of the sidewalk.</v>
       </c>
     </row>
-    <row r="211" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="31">
         <v>211</v>
       </c>
@@ -25930,7 +25862,7 @@
         <v>Continuous side protection element at the edge of the high-speed road.</v>
       </c>
     </row>
-    <row r="212" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="31">
         <v>212</v>
       </c>
@@ -26022,7 +25954,7 @@
         <v>Structure subject to the action of load in motion, with variable positioning, here called mobile load, used to overcome a natural obstacle (river, stream, valley, etc.).</v>
       </c>
     </row>
-    <row r="213" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="31">
         <v>213</v>
       </c>
@@ -26114,7 +26046,7 @@
         <v>Elevated structure so that vehicles can overcome an artificial obstacle such as an avenue, highway, etc.</v>
       </c>
     </row>
-    <row r="214" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="31">
         <v>214</v>
       </c>
@@ -26206,7 +26138,7 @@
         <v>Elevated and elongated structure, intended for pedestrians to overcome natural and/or artificial obstacles. Exclusively for pedestrians and/or cyclists.</v>
       </c>
     </row>
-    <row r="215" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="31">
         <v>215</v>
       </c>
@@ -26298,7 +26230,7 @@
         <v>An underpass that allows people, vehicles, or trains to move through natural or urban obstacles.</v>
       </c>
     </row>
-    <row r="216" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="31">
         <v>216</v>
       </c>
@@ -26390,7 +26322,7 @@
         <v>Subfluvial or maritime passage that allows the movement of people, vehicles or trains.</v>
       </c>
     </row>
-    <row r="217" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="31">
         <v>217</v>
       </c>
@@ -26482,7 +26414,7 @@
         <v>Buildings with any floor, with several floors, with access ramps or elevators intended for the parking of light vehicles, for low-speed circulation.</v>
       </c>
     </row>
-    <row r="218" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="31">
         <v>218</v>
       </c>
@@ -26574,7 +26506,7 @@
         <v>Part of a Special Work of Art: A type of structural element generally used to transmit the loads from the deck to the pylon.</v>
       </c>
     </row>
-    <row r="219" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="31">
         <v>219</v>
       </c>
@@ -26666,7 +26598,7 @@
         <v>Part of a Special Artwork: Bridge foundation piles.</v>
       </c>
     </row>
-    <row r="220" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="31">
         <v>220</v>
       </c>
@@ -26758,7 +26690,7 @@
         <v>Part of a Special Artwork: Bridge Foundation Blocks.</v>
       </c>
     </row>
-    <row r="221" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="31">
         <v>221</v>
       </c>
@@ -26850,7 +26782,7 @@
         <v>Part of a Special Work of Art: Structure where the road network meets the bridge heads.</v>
       </c>
     </row>
-    <row r="222" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="31">
         <v>222</v>
       </c>
@@ -26942,7 +26874,7 @@
         <v>Part of a Special Work of Art: Pillars supporting the deck also called Pier.</v>
       </c>
     </row>
-    <row r="223" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="31">
         <v>223</v>
       </c>
@@ -27034,7 +26966,7 @@
         <v>Part of a Special Work of Art: Arched concrete structure to support the bridge.</v>
       </c>
     </row>
-    <row r="224" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="31">
         <v>224</v>
       </c>
@@ -27126,7 +27058,7 @@
         <v>Part of a Special Work of Art: Vertical concrete structure above the deck to support the bridge cables.</v>
       </c>
     </row>
-    <row r="225" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="31">
         <v>225</v>
       </c>
@@ -27218,7 +27150,7 @@
         <v>Part of a Special Work of Art: Vertical metallic structure above the deck to support the bridge cables.</v>
       </c>
     </row>
-    <row r="226" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="31">
         <v>226</v>
       </c>
@@ -27310,7 +27242,7 @@
         <v>Part of a Special Artwork: Segments of the bridge deck. The segments can be separated by construction or expansion joints.</v>
       </c>
     </row>
-    <row r="227" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="31">
         <v>227</v>
       </c>
@@ -27402,7 +27334,7 @@
         <v>Part of a Special Work of Art: Support cables of a cable-stayed bridge.</v>
       </c>
     </row>
-    <row r="228" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="31">
         <v>228</v>
       </c>
@@ -27494,7 +27426,7 @@
         <v>Part of a Special Work of Art: Main beams in the longitudinal direction at the edge of the bridge.</v>
       </c>
     </row>
-    <row r="229" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="31">
         <v>229</v>
       </c>
@@ -27586,7 +27518,7 @@
         <v>Part of a Special Work of Art: Main beams in the longitudinal direction inside the bridge.</v>
       </c>
     </row>
-    <row r="230" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="31">
         <v>230</v>
       </c>
@@ -27678,7 +27610,7 @@
         <v>Part of a Special Work of Art: Beams in the transverse direction of the bridge.</v>
       </c>
     </row>
-    <row r="231" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="31">
         <v>231</v>
       </c>
@@ -27770,7 +27702,7 @@
         <v>Part of a Special Artwork: Bracing of the bridge.</v>
       </c>
     </row>
-    <row r="232" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="31">
         <v>232</v>
       </c>
@@ -27862,7 +27794,7 @@
         <v>Part of a Special Work of Art: Walls in the transverse direction of the bridge.</v>
       </c>
     </row>
-    <row r="233" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="31">
         <v>233</v>
       </c>
@@ -27954,7 +27886,7 @@
         <v>Part of a Special Artwork: Bridge trusses.</v>
       </c>
     </row>
-    <row r="234" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="31">
         <v>234</v>
       </c>
@@ -28046,7 +27978,7 @@
         <v>Part of a Special Work of Art: Element of structural defense of the work of Special Art.</v>
       </c>
     </row>
-    <row r="235" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="31">
         <v>235</v>
       </c>
@@ -28138,7 +28070,7 @@
         <v>Part of a Special Work of Art: Asphalt layer of the road track of the deck.</v>
       </c>
     </row>
-    <row r="236" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="31">
         <v>236</v>
       </c>
@@ -28230,7 +28162,7 @@
         <v>Part of a Special Work of Art: Subfloor layer of the deck carriageway.</v>
       </c>
     </row>
-    <row r="237" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="31">
         <v>237</v>
       </c>
@@ -28322,7 +28254,7 @@
         <v>Part of a Special Work of Art: Road expansion joint of the deck.</v>
       </c>
     </row>
-    <row r="238" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A238" s="31">
         <v>238</v>
       </c>
@@ -28414,7 +28346,7 @@
         <v>Part of a Special Work of Art: Water drainage element on the bridge.</v>
       </c>
     </row>
-    <row r="239" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A239" s="31">
         <v>239</v>
       </c>
@@ -28506,7 +28438,7 @@
         <v>Part of a Special Work of Art: Signage element type information plates.</v>
       </c>
     </row>
-    <row r="240" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A240" s="31">
         <v>240</v>
       </c>
@@ -28598,7 +28530,7 @@
         <v>Part of a Special Artwork: Lamppost-like lighting element.</v>
       </c>
     </row>
-    <row r="241" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A241" s="31">
         <v>241</v>
       </c>
@@ -28690,7 +28622,7 @@
         <v>Railway system designed to travel at high speed.</v>
       </c>
     </row>
-    <row r="242" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A242" s="31">
         <v>242</v>
       </c>
@@ -28782,7 +28714,7 @@
         <v>A railway that starts from a capital city towards the extremes of the country.</v>
       </c>
     </row>
-    <row r="243" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A243" s="31">
         <v>243</v>
       </c>
@@ -28874,7 +28806,7 @@
         <v>A railroad that crosses a country in a North-South direction.</v>
       </c>
     </row>
-    <row r="244" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A244" s="31">
         <v>244</v>
       </c>
@@ -28966,7 +28898,7 @@
         <v>A railroad that crosses a country in an East-West direction.</v>
       </c>
     </row>
-    <row r="245" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="31">
         <v>245</v>
       </c>
@@ -29058,7 +28990,7 @@
         <v>A railroad that crosses a country with a northeast-southwest or northwest-southeast orientation.</v>
       </c>
     </row>
-    <row r="246" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="31">
         <v>246</v>
       </c>
@@ -29150,7 +29082,7 @@
         <v>A railroad that connects railroads to each other or to specific localities.</v>
       </c>
     </row>
-    <row r="247" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="31">
         <v>247</v>
       </c>
@@ -29242,7 +29174,7 @@
         <v>Urban railway. Usually underground, but may have stretches at the urban level.</v>
       </c>
     </row>
-    <row r="248" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="31">
         <v>248</v>
       </c>
@@ -29334,7 +29266,7 @@
         <v>Urban railway to VLT. It operates on the urban surface and meets accessibility requirements.</v>
       </c>
     </row>
-    <row r="249" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A249" s="31">
         <v>249</v>
       </c>
@@ -29426,7 +29358,7 @@
         <v>A railway system in which vehicles run on a single elevated rail that serves as both a guide and a structural support.</v>
       </c>
     </row>
-    <row r="250" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A250" s="31">
         <v>250</v>
       </c>
@@ -29518,7 +29450,7 @@
         <v>Tunnel for railroad passage.</v>
       </c>
     </row>
-    <row r="251" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A251" s="31">
         <v>251</v>
       </c>
@@ -29610,7 +29542,7 @@
         <v>Central station of the line. Large stations such as Central do Brasil, Leopoldina or Retiro.</v>
       </c>
     </row>
-    <row r="252" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A252" s="31">
         <v>252</v>
       </c>
@@ -29702,7 +29634,7 @@
         <v>Line terminal station.</v>
       </c>
     </row>
-    <row r="253" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="31">
         <v>253</v>
       </c>
@@ -29794,7 +29726,7 @@
         <v>Transfer station of the same modal.</v>
       </c>
     </row>
-    <row r="254" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="31">
         <v>254</v>
       </c>
@@ -29886,7 +29818,7 @@
         <v>Multimodal transfer station.</v>
       </c>
     </row>
-    <row r="255" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A255" s="31">
         <v>255</v>
       </c>
@@ -29978,7 +29910,7 @@
         <v>Train station.</v>
       </c>
     </row>
-    <row r="256" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A256" s="31">
         <v>256</v>
       </c>
@@ -30070,7 +30002,7 @@
         <v>Metro station.</v>
       </c>
     </row>
-    <row r="257" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A257" s="31">
         <v>257</v>
       </c>
@@ -30162,7 +30094,7 @@
         <v>Light rail station.</v>
       </c>
     </row>
-    <row r="258" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A258" s="31">
         <v>258</v>
       </c>
@@ -30254,7 +30186,7 @@
         <v>Monorail station.</v>
       </c>
     </row>
-    <row r="259" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A259" s="31">
         <v>259</v>
       </c>
@@ -30346,7 +30278,7 @@
         <v>Rail designed with the internal distance between rails of 1000 mm.</v>
       </c>
     </row>
-    <row r="260" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A260" s="31">
         <v>260</v>
       </c>
@@ -30438,7 +30370,7 @@
         <v>Rail designed with the internal distance between rails of 1435 mm.</v>
       </c>
     </row>
-    <row r="261" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A261" s="31">
         <v>261</v>
       </c>
@@ -30530,7 +30462,7 @@
         <v>Rail designed with the internal distance between rails of 1600 mm.</v>
       </c>
     </row>
-    <row r="262" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A262" s="31">
         <v>262</v>
       </c>
@@ -30622,7 +30554,7 @@
         <v>Railway track designed with International and Irish gauge.</v>
       </c>
     </row>
-    <row r="263" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A263" s="31">
         <v>263</v>
       </c>
@@ -30714,7 +30646,7 @@
         <v>The basic component of the railroad on which trains run.</v>
       </c>
     </row>
-    <row r="264" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="31">
         <v>264</v>
       </c>
@@ -30806,7 +30738,7 @@
         <v>It can refer to the cutting edge or profile of the rail, used in technical contexts.</v>
       </c>
     </row>
-    <row r="265" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A265" s="31">
         <v>265</v>
       </c>
@@ -30898,7 +30830,7 @@
         <v>Additional rail placed next to the main rail on sharp turns to prevent derailment.</v>
       </c>
     </row>
-    <row r="266" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A266" s="31">
         <v>266</v>
       </c>
@@ -30990,7 +30922,7 @@
         <v>Similar to checkrail, it protects against derailments, especially at bridges and crossings.</v>
       </c>
     </row>
-    <row r="267" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="31">
         <v>267</v>
       </c>
@@ -31082,7 +31014,7 @@
         <v>Used on cogwheel railways, where locomotives climb steep inclines with gears.</v>
       </c>
     </row>
-    <row r="268" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A268" s="31">
         <v>268</v>
       </c>
@@ -31174,7 +31106,7 @@
         <v>Part of the rail that remains fixed on turnouts, against which the moving rail rests.</v>
       </c>
     </row>
-    <row r="269" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A269" s="31">
         <v>269</v>
       </c>
@@ -31266,7 +31198,7 @@
         <v>A section that allows the train to change tracks, such as at crossings or detours.</v>
       </c>
     </row>
-    <row r="270" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A270" s="31">
         <v>270</v>
       </c>
@@ -31358,7 +31290,7 @@
         <v>Equipment that prevents the movement of trains under certain conditions.</v>
       </c>
     </row>
-    <row r="271" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="31">
         <v>271</v>
       </c>
@@ -31450,7 +31382,7 @@
         <v>Safety device that forces the train off the tracks in the event of an emergency.</v>
       </c>
     </row>
-    <row r="272" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="31">
         <v>272</v>
       </c>
@@ -31542,7 +31474,7 @@
         <v>Metal piece where the rails intersect in turnouts.</v>
       </c>
     </row>
-    <row r="273" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A273" s="31">
         <v>273</v>
       </c>
@@ -31634,7 +31566,7 @@
         <v>Moving part of a Turnout Device (AMV) that directs the train to different tracks.</v>
       </c>
     </row>
-    <row r="274" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A274" s="31">
         <v>274</v>
       </c>
@@ -31726,7 +31658,7 @@
         <v>Transverse piece that supports the rails and distributes the load to the ballast.</v>
       </c>
     </row>
-    <row r="275" spans="1:27" s="52" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:27" s="52" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="31">
         <v>275</v>
       </c>
@@ -31818,7 +31750,7 @@
         <v>Equipment that controls the speed of trains, usually via signaling.</v>
       </c>
     </row>
-    <row r="276" spans="1:27" s="52" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:27" s="52" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="31">
         <v>276</v>
       </c>
@@ -31910,7 +31842,7 @@
         <v>End point of a railway section, where the route ends.</v>
       </c>
     </row>
-    <row r="277" spans="1:27" s="52" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:27" s="52" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="31">
         <v>277</v>
       </c>
@@ -32002,7 +31934,7 @@
         <v>A physical device that prevents movement beyond a safe point.</v>
       </c>
     </row>
-    <row r="278" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="31">
         <v>278</v>
       </c>
@@ -32094,7 +32026,7 @@
         <v>Individual elements that make up the railroad, such as rails and sleepers.</v>
       </c>
     </row>
-    <row r="279" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A279" s="31">
         <v>279</v>
       </c>
@@ -32186,7 +32118,7 @@
         <v>Railway barrier safety device installed at local level crossings where the railway line crosses urban or rural tracks.</v>
       </c>
     </row>
-    <row r="280" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A280" s="31">
         <v>280</v>
       </c>
@@ -32278,7 +32210,7 @@
         <v>Area next to the railroad, where equipment, signaling and infrastructure are located. Service range.</v>
       </c>
     </row>
-    <row r="281" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="31">
         <v>281</v>
       </c>
@@ -32370,7 +32302,7 @@
         <v>Aerial parts of the railway, such as signallers, electrification of railway wires, etc.</v>
       </c>
     </row>
-    <row r="282" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="31">
         <v>282</v>
       </c>
@@ -32462,7 +32394,7 @@
         <v>Elements such as poles, signs, control boxes next to the rails.</v>
       </c>
     </row>
-    <row r="283" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A283" s="31">
         <v>283</v>
       </c>
@@ -32554,7 +32486,7 @@
         <v>Railroad base: includes the bed, ballast, and foundations that support the tracks.</v>
       </c>
     </row>
-    <row r="284" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A284" s="31">
         <v>284</v>
       </c>
@@ -32646,7 +32578,7 @@
         <v>Straight and continuous stretch of the railroad, without switches and turnouts.</v>
       </c>
     </row>
-    <row r="285" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A285" s="31">
         <v>285</v>
       </c>
@@ -32738,7 +32670,7 @@
         <v>Complete set of rails, sleepers, fixings and base.</v>
       </c>
     </row>
-    <row r="286" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A286" s="31">
         <v>286</v>
       </c>
@@ -32830,7 +32762,7 @@
         <v>Section with special joints to accommodate the thermal expansion of the rails.</v>
       </c>
     </row>
-    <row r="287" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A287" s="31">
         <v>287</v>
       </c>
@@ -32922,7 +32854,7 @@
         <v>Fixed vertical structure that serves as a navigational mark, to show reefs or other hazards, or to provide.</v>
       </c>
     </row>
-    <row r="288" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A288" s="31">
         <v>288</v>
       </c>
@@ -33014,7 +32946,7 @@
         <v>Anchored floating structure that serves as a navigational mark, to show reefs or other hazards.</v>
       </c>
     </row>
-    <row r="289" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A289" s="31">
         <v>289</v>
       </c>
@@ -33106,7 +33038,7 @@
         <v>Buoy that assists maritime navigation, used to guide vessels, delimit channels, indicate hazards or special areas. Standardized by the IALA (International Association of Marine Aids to Navigation and Lighthouse Authorities) system.</v>
       </c>
     </row>
-    <row r="290" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A290" s="31">
         <v>290</v>
       </c>
@@ -33198,7 +33130,7 @@
         <v>Spatial part of the region that represents a managed area for the anchorage of vessels waiting for space in the port.</v>
       </c>
     </row>
-    <row r="291" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A291" s="31">
         <v>291</v>
       </c>
@@ -33290,7 +33222,7 @@
         <v>Longitudinal spatial part of a waterway or port facility that provides facilities for berthing.</v>
       </c>
     </row>
-    <row r="292" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A292" s="31">
         <v>292</v>
       </c>
@@ -33382,7 +33314,7 @@
         <v>Artificial watercourse usually built to join rivers, lakes or seas and often of an appropriate size.</v>
       </c>
     </row>
-    <row r="293" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A293" s="31">
         <v>293</v>
       </c>
@@ -33474,7 +33406,7 @@
         <v>The longitudinal spatial part of a waterway or port facility covering the approach.</v>
       </c>
     </row>
-    <row r="294" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A294" s="31">
         <v>294</v>
       </c>
@@ -33566,7 +33498,7 @@
         <v>Natural navigable watercourse (such as a river) that needs to be managed or have improvements applied.</v>
       </c>
     </row>
-    <row r="295" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A295" s="31">
         <v>295</v>
       </c>
@@ -33658,7 +33590,7 @@
         <v>Subset of facilities that have the primary function of providing a navigable area of water.</v>
       </c>
     </row>
-    <row r="296" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A296" s="31">
         <v>296</v>
       </c>
@@ -33750,7 +33682,7 @@
         <v>A navigation element is an active or passive constructed element whose primary function is to provide navigation.</v>
       </c>
     </row>
-    <row r="297" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A297" s="31">
         <v>297</v>
       </c>
@@ -33842,7 +33774,7 @@
         <v>A lashing device is an active or passive constructed element whose primary function is to participate in the lashing.</v>
       </c>
     </row>
-    <row r="298" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A298" s="31">
         <v>298</v>
       </c>
@@ -33934,7 +33866,7 @@
         <v>Quick release mooring hooks – an active device used to secure a vessel and provide automated release.</v>
       </c>
     </row>
-    <row r="299" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A299" s="31">
         <v>299</v>
       </c>
@@ -34026,7 +33958,7 @@
         <v>Short, thick post on a ship's deck or quayside, to which the ship's rope can be attached to keep the vessel safe and stable during berthing. The distance between them can vary from 5 to 10 meters.</v>
       </c>
     </row>
-    <row r="300" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A300" s="31">
         <v>300</v>
       </c>
@@ -34118,7 +34050,7 @@
         <v>A motorized mechanical device used to apply a tensioning load to mooring lines to improve the stability of the vessel.</v>
       </c>
     </row>
-    <row r="301" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A301" s="31">
         <v>301</v>
       </c>
@@ -34210,7 +34142,7 @@
         <v>A mechanical device used to apply a tensioning load to mooring lines to improve the stability of the vessel.</v>
       </c>
     </row>
-    <row r="302" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A302" s="31">
         <v>302</v>
       </c>
@@ -34302,7 +34234,7 @@
         <v>Mooring device that uses vacuum suction as the primary method of securing the vessel.</v>
       </c>
     </row>
-    <row r="303" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A303" s="31">
         <v>303</v>
       </c>
@@ -34394,7 +34326,7 @@
         <v>A mooring device that uses magnets as the primary method of securing the vessel.</v>
       </c>
     </row>
-    <row r="304" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A304" s="31">
         <v>304</v>
       </c>
@@ -34486,7 +34418,7 @@
         <v>SafeCom Ship-to-Shore (SSL) Connection System is a security communication system used for the transfer of hazardous liquids and gases.</v>
       </c>
     </row>
-    <row r="305" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A305" s="31">
         <v>305</v>
       </c>
@@ -34578,7 +34510,7 @@
         <v>Level that represents the elevation of the waterline at high tide.</v>
       </c>
     </row>
-    <row r="306" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A306" s="31">
         <v>306</v>
       </c>
@@ -34670,7 +34602,7 @@
         <v>Level that represents the elevation of the waterline at low tide.</v>
       </c>
     </row>
-    <row r="307" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A307" s="31">
         <v>307</v>
       </c>
@@ -34762,7 +34694,7 @@
         <v>Level that represents the part above the average waterline defined within the site area.</v>
       </c>
     </row>
-    <row r="308" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A308" s="31">
         <v>308</v>
       </c>
@@ -34854,7 +34786,7 @@
         <v>Level that represents the part below the average waterline defined within the site area.</v>
       </c>
     </row>
-    <row r="309" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A309" s="31">
         <v>309</v>
       </c>
@@ -34946,7 +34878,7 @@
         <v>Level that represents the minimum operating depth.</v>
       </c>
     </row>
-    <row r="310" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A310" s="31">
         <v>310</v>
       </c>
@@ -35038,7 +34970,7 @@
         <v>Level that represents the working floor of the pier, where the crane rails and the people working are located.</v>
       </c>
     </row>
-    <row r="311" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A311" s="31">
         <v>311</v>
       </c>
@@ -35130,7 +35062,7 @@
         <v>Reference level provided by hydrographic survey of the port.</v>
       </c>
     </row>
-    <row r="312" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A312" s="31">
         <v>312</v>
       </c>
@@ -35222,7 +35154,7 @@
         <v>Complex/facility to receive ships with a large draft. Built in a coastal area with direct access to the ocean, without the need for artificial channels or frequent dredging.</v>
       </c>
     </row>
-    <row r="313" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A313" s="31">
         <v>313</v>
       </c>
@@ -35314,7 +35246,7 @@
         <v>Complex/facility for maritime activities, which includes cargo, people and storage.</v>
       </c>
     </row>
-    <row r="314" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A314" s="31">
         <v>314</v>
       </c>
@@ -35406,7 +35338,7 @@
         <v>Complex/facility for maritime activities, which includes cargo, people and storage.</v>
       </c>
     </row>
-    <row r="315" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A315" s="31">
         <v>315</v>
       </c>
@@ -35498,7 +35430,7 @@
         <v>Complex/facility for river activities, which includes cargo, people and storage.</v>
       </c>
     </row>
-    <row r="316" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A316" s="31">
         <v>316</v>
       </c>
@@ -35590,7 +35522,7 @@
         <v>Line where there is a decrease in the energy of the sea waves.</v>
       </c>
     </row>
-    <row r="317" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A317" s="31">
         <v>317</v>
       </c>
@@ -35682,7 +35614,7 @@
         <v>A structure built to protect the coast, ports or urban areas from the force of waves and sea currents, it can be parallel or perpendicular to the coast.</v>
       </c>
     </row>
-    <row r="318" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A318" s="31">
         <v>318</v>
       </c>
@@ -35774,7 +35706,7 @@
         <v>Protection device that absorbs the impact between the ship and the quay.</v>
       </c>
     </row>
-    <row r="319" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A319" s="31">
         <v>319</v>
       </c>
@@ -35866,7 +35798,7 @@
         <v>Marine defensive structure made of earthworks, masonry and rocks.</v>
       </c>
     </row>
-    <row r="320" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A320" s="31">
         <v>320</v>
       </c>
@@ -35958,7 +35890,7 @@
         <v>The dry dock is a closed chamber (by gate) that allows the drainage of water into the building.</v>
       </c>
     </row>
-    <row r="321" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A321" s="31">
         <v>321</v>
       </c>
@@ -36050,7 +35982,7 @@
         <v>Space element that encompasses a floating dry dock and lateral support quay auxiliaries.</v>
       </c>
     </row>
-    <row r="322" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A322" s="31">
         <v>322</v>
       </c>
@@ -36142,7 +36074,7 @@
         <v>Marine facility represents any major structure or entity that is specific to ports and waters.</v>
       </c>
     </row>
-    <row r="323" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A323" s="31">
         <v>323</v>
       </c>
@@ -36234,7 +36166,7 @@
         <v>A mountain range of sand that rises slightly above the surface of the sea and runs roughly parallel to the coast.</v>
       </c>
     </row>
-    <row r="324" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A324" s="31">
         <v>324</v>
       </c>
@@ -36326,7 +36258,7 @@
         <v>A type of vessel launch recovery facility, also known as a hydraulic lifting dock, where ships are lifted.</v>
       </c>
     </row>
-    <row r="325" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A325" s="31">
         <v>325</v>
       </c>
@@ -36418,7 +36350,7 @@
         <v>Place for mooring vessels without contact with the shore of the coast.</v>
       </c>
     </row>
-    <row r="326" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A326" s="31">
         <v>326</v>
       </c>
@@ -36510,7 +36442,7 @@
         <v>Place for the mooring of vessels accompanied by elements for loading and unloading products or people positioned perpendicular to the coast.</v>
       </c>
     </row>
-    <row r="327" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A327" s="31">
         <v>327</v>
       </c>
@@ -36602,7 +36534,7 @@
         <v>Place for the mooring of vessels accompanied by elements for loading and unloading products or people positioned parallel to the coast.</v>
       </c>
     </row>
-    <row r="328" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A328" s="31">
         <v>328</v>
       </c>
@@ -36694,7 +36626,7 @@
         <v>Water space that the ship occupies when it docks at the pier. The submerged wall and bed should be designed to minimize erosion and sedimentation processes.</v>
       </c>
     </row>
-    <row r="329" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A329" s="31">
         <v>329</v>
       </c>
@@ -36786,7 +36718,7 @@
         <v>A type of vessel launch recovery facility, where ships are lifted vertically out of the water.</v>
       </c>
     </row>
-    <row r="330" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A330" s="31">
         <v>330</v>
       </c>
@@ -36878,7 +36810,7 @@
         <v>Facility used to raise and lower boats, ships, and other vessels between stretches of water.</v>
       </c>
     </row>
-    <row r="331" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A331" s="31">
         <v>331</v>
       </c>
@@ -36970,7 +36902,7 @@
         <v>Coastal/waterfront facility where ships are built and repaired.</v>
       </c>
     </row>
-    <row r="332" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A332" s="31">
         <v>332</v>
       </c>
@@ -37062,7 +36994,7 @@
         <v>Installation for the dynamic launch or recovery of a vessel using an inclined ramp and gravitation.</v>
       </c>
     </row>
-    <row r="333" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A333" s="31">
         <v>333</v>
       </c>
@@ -37154,7 +37086,7 @@
         <v>Subset of facilities for the ship launching or recovery function.</v>
       </c>
     </row>
-    <row r="334" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A334" s="31">
         <v>334</v>
       </c>
@@ -37246,7 +37178,7 @@
         <v>The longitudinal spatial part of a waterway or port facility that forms the dammed chamber.</v>
       </c>
     </row>
-    <row r="335" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A335" s="31">
         <v>335</v>
       </c>
@@ -37338,7 +37270,7 @@
         <v>A lateral spatial part that subdivides the central structure of a facility, such as a breakwater.</v>
       </c>
     </row>
-    <row r="336" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A336" s="31">
         <v>336</v>
       </c>
@@ -37430,7 +37362,7 @@
         <v>Lateral spatial part that forms the area of the ridge of the breakwater or embankment where additional structures.</v>
       </c>
     </row>
-    <row r="337" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A337" s="31">
         <v>337</v>
       </c>
@@ -37522,7 +37454,7 @@
         <v>The longitudinal spatial part of a waterway or port facility that forms the gate, the supporting structure.</v>
       </c>
     </row>
-    <row r="338" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A338" s="31">
         <v>338</v>
       </c>
@@ -37614,7 +37546,7 @@
         <v>Standardized metal rectangular structure mainly used for the transportation of goods.</v>
       </c>
     </row>
-    <row r="339" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A339" s="31">
         <v>339</v>
       </c>
@@ -37706,7 +37638,7 @@
         <v>Spatial part of the structure that is on the side exposed to the prevailing wind.</v>
       </c>
     </row>
-    <row r="340" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A340" s="31">
         <v>340</v>
       </c>
@@ -37798,7 +37730,7 @@
         <v>Spatial part of the structure that is protected from the prevailing wind.</v>
       </c>
     </row>
-    <row r="341" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A341" s="31">
         <v>341</v>
       </c>
@@ -37890,7 +37822,7 @@
         <v>Region that covers the water field of a port. It includes navigable and non-navigable canals.</v>
       </c>
     </row>
-    <row r="342" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A342" s="31">
         <v>342</v>
       </c>
@@ -37982,7 +37914,7 @@
         <v>Region or side part of the facility that covers the onshore field of seaside installation, such as a wharf.</v>
       </c>
     </row>
-    <row r="343" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A343" s="31">
         <v>343</v>
       </c>
@@ -38074,7 +38006,7 @@
         <v>Region that covers the water field of the harbor's navigable canals.</v>
       </c>
     </row>
-    <row r="344" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A344" s="31">
         <v>344</v>
       </c>
@@ -38166,7 +38098,7 @@
         <v>Covered space such as shed or storage for cargo storage.</v>
       </c>
     </row>
-    <row r="345" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A345" s="31">
         <v>345</v>
       </c>
@@ -38258,7 +38190,7 @@
         <v>External cargo storage space.</v>
       </c>
     </row>
-    <row r="346" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A346" s="31">
         <v>346</v>
       </c>
@@ -38350,7 +38282,7 @@
         <v>Spatial part of the region that represents a functional division designed for operation.</v>
       </c>
     </row>
-    <row r="347" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A347" s="31">
         <v>347</v>
       </c>
@@ -38442,7 +38374,7 @@
         <v>Spatial part of the region that forms a subdivision of facility for manufacturing purposes.</v>
       </c>
     </row>
-    <row r="348" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A348" s="31">
         <v>348</v>
       </c>
@@ -38534,7 +38466,7 @@
         <v>Spatial part of the region that represents a free area used for the transfer and movement of vessels.</v>
       </c>
     </row>
-    <row r="349" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A349" s="31">
         <v>349</v>
       </c>
@@ -38626,7 +38558,7 @@
         <v>International Airport must have infrastructure for international flights, with customs, immigration and sanitary control.</v>
       </c>
     </row>
-    <row r="350" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A350" s="31">
         <v>350</v>
       </c>
@@ -38718,7 +38650,7 @@
         <v>Regional airports serve smaller areas of the territory, connecting medium and small cities to large centers.</v>
       </c>
     </row>
-    <row r="351" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A351" s="31">
         <v>351</v>
       </c>
@@ -38810,7 +38742,7 @@
         <v>Domestic Airport only serves flights within the national territory.</v>
       </c>
     </row>
-    <row r="352" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A352" s="31">
         <v>352</v>
       </c>
@@ -38902,7 +38834,7 @@
         <v>Military Airport. used exclusively by the Armed Forces for strategic purposes, training, troop transport, and equipment.</v>
       </c>
     </row>
-    <row r="353" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A353" s="31">
         <v>353</v>
       </c>
@@ -38994,7 +38926,7 @@
         <v>A center for the education and training of civilian pilots, for practical or recreational purposes. It needs to be authorized by the National Civil Aviation Agency (ANAC) to operate legally.</v>
       </c>
     </row>
-    <row r="354" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A354" s="31">
         <v>354</v>
       </c>
@@ -39086,7 +39018,7 @@
         <v>The landing and takeoff runway comprises the rectangular area, defined on land, prepared for aircraft landings and takeoffs. Brazilian Civil Aviation Regulation (RBAC).</v>
       </c>
     </row>
-    <row r="355" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A355" s="31">
         <v>355</v>
       </c>
@@ -39178,7 +39110,7 @@
         <v>Auxiliary runways allow aircraft to move before taking off or after landing and speed up their traffic on the ground.</v>
       </c>
     </row>
-    <row r="356" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A356" s="31">
         <v>356</v>
       </c>
@@ -39270,7 +39202,7 @@
         <v>A Heliport must be prepared to operate helicopters with airstrip infrastructure, hangars, fueling, departure lounge, air traffic control, maintenance, security and logistics.</v>
       </c>
     </row>
-    <row r="357" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A357" s="31">
         <v>357</v>
       </c>
@@ -39362,7 +39294,7 @@
         <v>Area intended exclusively for helicopter landing and takeoff.</v>
       </c>
     </row>
-    <row r="358" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A358" s="31">
         <v>358</v>
       </c>
@@ -39454,7 +39386,7 @@
         <v>Drinking water supply network system.</v>
       </c>
     </row>
-    <row r="359" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A359" s="31">
         <v>359</v>
       </c>
@@ -39546,7 +39478,7 @@
         <v>A network system for the supply of substances (e.g. fuels).</v>
       </c>
     </row>
-    <row r="360" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A360" s="31">
         <v>360</v>
       </c>
@@ -39638,7 +39570,7 @@
         <v>Fuel supply network system.</v>
       </c>
     </row>
-    <row r="361" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A361" s="31">
         <v>361</v>
       </c>
@@ -39730,7 +39662,7 @@
         <v>Gas supply network system.</v>
       </c>
     </row>
-    <row r="362" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A362" s="31">
         <v>362</v>
       </c>
@@ -39822,7 +39754,7 @@
         <v>System of operational substances (fuels, hospital fluids, etc.).</v>
       </c>
     </row>
-    <row r="363" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A363" s="31">
         <v>363</v>
       </c>
@@ -39914,7 +39846,7 @@
         <v>Urban rainwater system (storm water that runs across the urban surface).</v>
       </c>
     </row>
-    <row r="364" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A364" s="31">
         <v>364</v>
       </c>
@@ -40006,7 +39938,7 @@
         <v>Recycling water system (water that has been negatively affected by anthropogenic influence).</v>
       </c>
     </row>
-    <row r="365" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A365" s="31">
         <v>365</v>
       </c>
@@ -40098,7 +40030,7 @@
         <v>Urban sewage collection system.</v>
       </c>
     </row>
-    <row r="366" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A366" s="31">
         <v>366</v>
       </c>
@@ -40190,7 +40122,7 @@
         <v>Sewage system for substances (special substances, for example).</v>
       </c>
     </row>
-    <row r="367" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A367" s="31">
         <v>367</v>
       </c>
@@ -40282,7 +40214,7 @@
         <v>Hospital gas or liquid network system.</v>
       </c>
     </row>
-    <row r="368" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A368" s="31">
         <v>368</v>
       </c>
@@ -40374,7 +40306,7 @@
         <v>High Voltage transmission power line with more than 69 kV.</v>
       </c>
     </row>
-    <row r="369" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A369" s="31">
         <v>369</v>
       </c>
@@ -40466,7 +40398,7 @@
         <v>Metal support structure of the High Voltage transmission power line with more than 69 kV.</v>
       </c>
     </row>
-    <row r="370" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A370" s="31">
         <v>370</v>
       </c>
@@ -40558,7 +40490,7 @@
         <v>Physical structure of EE distribution circuits. Posts, supports with insulators and bare conductors of aluminum or copper on pin or rod insulators on concrete crossarms.</v>
       </c>
     </row>
-    <row r="371" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A371" s="31">
         <v>371</v>
       </c>
@@ -40650,7 +40582,7 @@
         <v>Physical structure of EE distribution circuits. Poles, supports with insulators and aluminium conductors covered by a layer of insulation, grouped in bundles.</v>
       </c>
     </row>
-    <row r="372" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A372" s="31">
         <v>372</v>
       </c>
@@ -40742,7 +40674,7 @@
         <v>Physical structure of compact EE distribution circuits. Poles, supports with insulators and aluminium conductors covered by a layer of insulation, grouped in bundles.</v>
       </c>
     </row>
-    <row r="373" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A373" s="31">
         <v>373</v>
       </c>
@@ -40834,7 +40766,7 @@
         <v>See NBR 8451. Circular section concrete pole to conduct Medium Voltage overhead power grid.</v>
       </c>
     </row>
-    <row r="374" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A374" s="31">
         <v>374</v>
       </c>
@@ -40926,7 +40858,7 @@
         <v>See NBR 8451. Double Tee (DT) section concrete pole to conduct Medium Voltage overhead power grid.</v>
       </c>
     </row>
-    <row r="375" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A375" s="31">
         <v>375</v>
       </c>
@@ -41018,7 +40950,7 @@
         <v>Medium Voltage underground electrical network between 1 kV and 69 kV.</v>
       </c>
     </row>
-    <row r="376" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A376" s="31">
         <v>376</v>
       </c>
@@ -41110,7 +41042,7 @@
         <v>Low Voltage overhead power grid up to 1,000 volts (1Kv).</v>
       </c>
     </row>
-    <row r="377" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A377" s="31">
         <v>377</v>
       </c>
@@ -41202,7 +41134,7 @@
         <v>Low Voltage underground electrical network up to 1,000 volts (1Kv).</v>
       </c>
     </row>
-    <row r="378" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A378" s="31">
         <v>378</v>
       </c>
@@ -41294,7 +41226,7 @@
         <v>Consult NBR 5410 Standard. Point of connection of the electrical system of the electricity distribution company with the electrical installation of the consumer unit(s) and which delimits the responsibilities of the distributor, defined by the regulatory authority.</v>
       </c>
     </row>
-    <row r="379" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A379" s="31">
         <v>379</v>
       </c>
@@ -41386,7 +41318,7 @@
         <v>Consult NBR 5410 Standard. Point at which an external line penetrates the building.</v>
       </c>
     </row>
-    <row r="380" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A380" s="31">
         <v>380</v>
       </c>
@@ -41478,7 +41410,7 @@
         <v>Consult NBR 5410 Standard. The point of the supply is directly grounded, with the masses connected to this point by protective conductors. Three variants of TN scheme are considered, according to the arrangement of the neutral conductor and the protective conductor: TN-S scheme, the neutral conductor and the protective conductor are distinct; TN-C-S scheme, neutral and protection functions are combined in a single conductor; In the TN-C scheme, the neutral and protection functions are combined in a single conductor in the entire scheme.</v>
       </c>
     </row>
-    <row r="381" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A381" s="31">
         <v>381</v>
       </c>
@@ -41570,7 +41502,7 @@
         <v>Consult NBR 5410 Standard. Directly grounded supply point, with the installation grounds connected to grounding electrode(s) electrically distinct from the grounding electrode of the supply</v>
       </c>
     </row>
-    <row r="382" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A382" s="31">
         <v>382</v>
       </c>
@@ -41662,7 +41594,7 @@
         <v>Consult NBR 5410 Standard. All living parts are isolated from the earth or a feed point is grounded via impedance. The masses of the installation are grounded.</v>
       </c>
     </row>
-    <row r="383" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A383" s="31">
         <v>383</v>
       </c>
@@ -41754,7 +41686,7 @@
         <v>Urban public lighting electrical network.</v>
       </c>
     </row>
-    <row r="384" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A384" s="31">
         <v>384</v>
       </c>
@@ -41846,7 +41778,7 @@
         <v>Urban public signaling electrical network (traffic signals and totems).</v>
       </c>
     </row>
-    <row r="385" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A385" s="31">
         <v>385</v>
       </c>
@@ -41938,7 +41870,7 @@
         <v>Aerial Fiber Optic Network.</v>
       </c>
     </row>
-    <row r="386" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A386" s="31">
         <v>386</v>
       </c>
@@ -42030,7 +41962,7 @@
         <v>Underground telephone network.</v>
       </c>
     </row>
-    <row r="387" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A387" s="31">
         <v>387</v>
       </c>
@@ -42122,7 +42054,7 @@
         <v>Network data overhead logic.</v>
       </c>
     </row>
-    <row r="388" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A388" s="31">
         <v>388</v>
       </c>
@@ -42214,7 +42146,7 @@
         <v>Network data underground logic.</v>
       </c>
     </row>
-    <row r="389" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A389" s="31">
         <v>389</v>
       </c>
@@ -42306,7 +42238,7 @@
         <v>Aerial Mobile Internet Network.</v>
       </c>
     </row>
-    <row r="390" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A390" s="31">
         <v>390</v>
       </c>
@@ -42398,7 +42330,7 @@
         <v>Aerial Fixed Internet Network.</v>
       </c>
     </row>
-    <row r="391" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A391" s="31">
         <v>391</v>
       </c>
@@ -42490,7 +42422,7 @@
         <v>Underground Fixed Internet Network.</v>
       </c>
     </row>
-    <row r="392" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A392" s="31">
         <v>392</v>
       </c>
@@ -42582,7 +42514,7 @@
         <v>Air telephone network.</v>
       </c>
     </row>
-    <row r="393" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A393" s="31">
         <v>393</v>
       </c>
@@ -42677,132 +42609,132 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:A393">
-    <cfRule type="cellIs" dxfId="76" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1 F14:F31 F349:F357 F394:F1048576 A1:D1 L1:Q1 S1:W1 AB1:XFD1 B7:B13 L14:Q18 B14:D20 S14:U30 AB14:XFD31 L19:O21 Q19:Q21 B21:C25 D21:D42 L22:Q31 B26:B31 C26:C42 S31:T31 U31:U42 O32:O42 L349:P357 C358:C393 A394:D1048576 L394:Q1048576 S394:W1048576 AA394:XFD1048576">
-    <cfRule type="cellIs" dxfId="75" priority="378" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="378" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="74" priority="1416"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="73" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F13">
-    <cfRule type="duplicateValues" dxfId="69" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F33">
-    <cfRule type="duplicateValues" dxfId="67" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F42">
-    <cfRule type="duplicateValues" dxfId="65" priority="955"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="955"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34:F42">
-    <cfRule type="duplicateValues" dxfId="64" priority="957"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="958"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="959"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="960"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="957"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="960"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="959"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="958"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43:F100 F14:F31">
-    <cfRule type="duplicateValues" dxfId="60" priority="1308"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="1308"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43:F348 L43:Q348 B43:D357 AB43:XFD357 S43:U393 B358">
-    <cfRule type="cellIs" dxfId="59" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101:F110">
-    <cfRule type="duplicateValues" dxfId="58" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F118:F121">
-    <cfRule type="duplicateValues" dxfId="56" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F145:F163">
-    <cfRule type="duplicateValues" dxfId="54" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F145:F179">
-    <cfRule type="duplicateValues" dxfId="53" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F179">
-    <cfRule type="duplicateValues" dxfId="52" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F180:F189">
-    <cfRule type="duplicateValues" dxfId="51" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F190:F211 F111:F117 F122:F144">
-    <cfRule type="duplicateValues" dxfId="50" priority="1244"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="1244"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F212:F217">
-    <cfRule type="duplicateValues" dxfId="49" priority="572"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="572"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F287:F295">
-    <cfRule type="duplicateValues" dxfId="48" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F287:F357">
-    <cfRule type="duplicateValues" dxfId="47" priority="1622"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1622"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296">
-    <cfRule type="duplicateValues" dxfId="46" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F297">
-    <cfRule type="duplicateValues" dxfId="45" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="448"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="449"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="451"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="448"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F298:F304">
-    <cfRule type="duplicateValues" dxfId="38" priority="741"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="741"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F320:F324 F305:F311 F316:F317">
-    <cfRule type="duplicateValues" dxfId="37" priority="455"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F338">
-    <cfRule type="duplicateValues" dxfId="36" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F358:F384">
-    <cfRule type="duplicateValues" dxfId="35" priority="1581"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="1582"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1581"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F385:F393">
-    <cfRule type="duplicateValues" dxfId="33" priority="1656"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="1657"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1657"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F394:F1048576 F1 F14:F357">
-    <cfRule type="duplicateValues" dxfId="31" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F394:F1048576 F1 F43:F357 F14:F31">
-    <cfRule type="duplicateValues" dxfId="29" priority="895"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="914"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="895"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="914"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F394:F1048576 F1 F101:F117 F122:F144 F190:F286">
-    <cfRule type="duplicateValues" dxfId="27" priority="910"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="910"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F394:F1048576 F1 F101:F179 F190:F357">
-    <cfRule type="duplicateValues" dxfId="26" priority="898"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="898"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F394:F1048576 F1 F190:F217 F111:F117 F122:F144">
-    <cfRule type="duplicateValues" dxfId="25" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="902"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F394:F1048576 F1 F190:F240 F101:F117 F122:F144">
-    <cfRule type="duplicateValues" dxfId="24" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="906"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA393">
-    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -42816,15 +42748,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>22</v>
       </c>
@@ -42889,7 +42821,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24">
         <v>2</v>
       </c>
@@ -42954,7 +42886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="24">
         <v>3</v>
       </c>
@@ -43022,7 +42954,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43034,14 +42966,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -43055,7 +42987,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="52" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" s="52" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13">
         <v>2</v>
       </c>
@@ -43069,7 +43001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="52" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" s="52" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>3</v>
       </c>
@@ -43083,7 +43015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="52" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" s="52" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>4</v>
       </c>
@@ -43097,7 +43029,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="52" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" s="52" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>5</v>
       </c>
@@ -43111,7 +43043,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="52" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" s="52" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>6</v>
       </c>
@@ -43125,7 +43057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13">
         <v>7</v>
       </c>
@@ -43139,7 +43071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="13">
         <v>8</v>
       </c>
@@ -43153,7 +43085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13">
         <v>9</v>
       </c>
@@ -43167,7 +43099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13">
         <v>10</v>
       </c>
@@ -43181,7 +43113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13">
         <v>11</v>
       </c>
@@ -43195,7 +43127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13">
         <v>12</v>
       </c>
@@ -43209,7 +43141,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13">
         <v>13</v>
       </c>
@@ -43225,30 +43157,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A13">
-    <cfRule type="cellIs" dxfId="21" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:B10">
-    <cfRule type="duplicateValues" dxfId="20" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:B13">
-    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:C13">
-    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:C10">
-    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C13">
-    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -43257,67 +43189,68 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}">
   <dimension ref="A1:BE10"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="90" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" style="26" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.42578125" style="26" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="26" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" style="26" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="26" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="26" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" style="26" customWidth="1"/>
-    <col min="12" max="12" width="2.85546875" style="26" customWidth="1"/>
-    <col min="13" max="13" width="3" style="26" customWidth="1"/>
-    <col min="14" max="14" width="5.140625" style="26" customWidth="1"/>
-    <col min="15" max="15" width="26.5703125" style="26" customWidth="1"/>
-    <col min="16" max="17" width="3.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.85546875" style="26" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.85546875" style="26" customWidth="1"/>
-    <col min="24" max="24" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.85546875" style="70" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.85546875" style="70" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.85546875" style="70" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.85546875" style="91" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.85546875" style="91" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="3.85546875" style="91" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="3.85546875" style="91" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="3.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.85546875" style="91" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="3.85546875" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="3.85546875" style="70" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="7.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.42578125" style="26" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.85546875" style="70" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="5.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="16.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="5.85546875" style="70" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="5.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="9.7109375" style="70" bestFit="1" customWidth="1"/>
-    <col min="58" max="16384" width="9.140625" style="26"/>
+    <col min="1" max="1" width="2.53515625" style="90" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.921875" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.07421875" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.765625" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.3828125" style="26" customWidth="1"/>
+    <col min="6" max="6" width="6.15234375" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.921875" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.61328125" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.921875" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.61328125" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.84375" style="26" customWidth="1"/>
+    <col min="12" max="12" width="2.3828125" style="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.15234375" style="26" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.53515625" style="26" customWidth="1"/>
+    <col min="16" max="17" width="3.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.84375" style="26" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.53515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.84375" style="26" customWidth="1"/>
+    <col min="24" max="24" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.84375" style="70" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.84375" style="70" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.84375" style="70" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.84375" style="91" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.84375" style="91" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="3.84375" style="91" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="3.84375" style="91" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="3.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.84375" style="91" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="3.84375" style="70" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="3.84375" style="70" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.3046875" style="70" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.3828125" style="26" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.84375" style="70" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="5.69140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="16.3046875" style="70" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="5.84375" style="70" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="5.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="9.69140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="58" max="16384" width="9.15234375" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="30" t="s">
         <v>74</v>
       </c>
@@ -43486,7 +43419,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="60">
         <v>2</v>
       </c>
@@ -43659,7 +43592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="60">
         <v>3</v>
       </c>
@@ -43829,11 +43762,11 @@
         <v>1461</v>
       </c>
       <c r="BE3" s="62" t="str">
-        <f>_xlfn.CONCAT("""",C3,"""")</f>
+        <f t="shared" ref="BE3:BE10" si="0">_xlfn.CONCAT("""",C3,"""")</f>
         <v>"SubContinente"</v>
       </c>
     </row>
-    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="60">
         <v>4</v>
       </c>
@@ -44003,11 +43936,11 @@
         <v>1461</v>
       </c>
       <c r="BE4" s="62" t="str">
-        <f>_xlfn.CONCAT("""",C4,"""")</f>
+        <f t="shared" si="0"/>
         <v>"País"</v>
       </c>
     </row>
-    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="60">
         <v>5</v>
       </c>
@@ -44177,11 +44110,11 @@
         <v>1461</v>
       </c>
       <c r="BE5" s="62" t="str">
-        <f>_xlfn.CONCAT("""",C5,"""")</f>
+        <f t="shared" si="0"/>
         <v>"Região"</v>
       </c>
     </row>
-    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="60">
         <v>6</v>
       </c>
@@ -44351,11 +44284,11 @@
         <v>1461</v>
       </c>
       <c r="BE6" s="62" t="str">
-        <f>_xlfn.CONCAT("""",C6,"""")</f>
+        <f t="shared" si="0"/>
         <v>"Região"</v>
       </c>
     </row>
-    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="60">
         <v>7</v>
       </c>
@@ -44525,43 +44458,43 @@
         <v>1461</v>
       </c>
       <c r="BE7" s="62" t="str">
-        <f>_xlfn.CONCAT("""",C7,"""")</f>
+        <f t="shared" si="0"/>
         <v>"Estado"</v>
       </c>
     </row>
-    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="60">
         <v>8</v>
       </c>
       <c r="B8" s="95" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>631</v>
-      </c>
-      <c r="D8" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="D8" s="67" t="s">
         <v>737</v>
       </c>
-      <c r="E8" s="63" t="s">
-        <v>740</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>1</v>
+      <c r="E8" s="68" t="s">
+        <v>746</v>
+      </c>
+      <c r="F8" s="67" t="s">
+        <v>737</v>
+      </c>
+      <c r="G8" s="68" t="s">
+        <v>747</v>
+      </c>
+      <c r="H8" s="67" t="s">
+        <v>743</v>
+      </c>
+      <c r="I8" s="68" t="s">
+        <v>748</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>1</v>
+        <v>744</v>
+      </c>
+      <c r="K8" s="63" t="s">
+        <v>742</v>
       </c>
       <c r="L8" s="19" t="s">
         <v>1</v>
@@ -44572,8 +44505,9 @@
       <c r="N8" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="O8" s="40" t="s">
-        <v>1477</v>
+      <c r="O8" s="29" t="str">
+        <f>_xlfn.CONCAT("""É a cidade capital do Estado de ",K8," do Brasil """)</f>
+        <v>"É a cidade capital do Estado de Minas.Gerais do Brasil "</v>
       </c>
       <c r="P8" s="61" t="s">
         <v>1</v>
@@ -44582,22 +44516,22 @@
         <v>1</v>
       </c>
       <c r="R8" s="61" t="s">
-        <v>755</v>
-      </c>
-      <c r="S8" s="69" t="s">
-        <v>759</v>
+        <v>1</v>
+      </c>
+      <c r="S8" s="66" t="s">
+        <v>1</v>
       </c>
       <c r="T8" s="61" t="s">
-        <v>756</v>
-      </c>
-      <c r="U8" s="64" t="s">
-        <v>760</v>
+        <v>1</v>
+      </c>
+      <c r="U8" s="40" t="s">
+        <v>1</v>
       </c>
       <c r="V8" s="61" t="s">
-        <v>757</v>
-      </c>
-      <c r="W8" s="29" t="s">
-        <v>761</v>
+        <v>1</v>
+      </c>
+      <c r="W8" s="40" t="s">
+        <v>1</v>
       </c>
       <c r="X8" s="61" t="s">
         <v>1</v>
@@ -44672,22 +44606,22 @@
         <v>1</v>
       </c>
       <c r="AV8" s="46" t="s">
-        <v>1</v>
+        <v>1473</v>
       </c>
       <c r="AW8" s="62" t="s">
-        <v>1</v>
+        <v>1474</v>
       </c>
       <c r="AX8" s="46" t="s">
         <v>1333</v>
       </c>
       <c r="AY8" s="62" t="s">
-        <v>1464</v>
+        <v>1475</v>
       </c>
       <c r="AZ8" s="46" t="s">
         <v>764</v>
       </c>
       <c r="BA8" s="62" t="s">
-        <v>1464</v>
+        <v>1476</v>
       </c>
       <c r="BB8" s="46" t="s">
         <v>1460</v>
@@ -44699,16 +44633,16 @@
         <v>1461</v>
       </c>
       <c r="BE8" s="62" t="str">
-        <f>_xlfn.CONCAT("""",C8,"""")</f>
-        <v>"UF"</v>
+        <f t="shared" ref="BE8" si="1">_xlfn.CONCAT("""",C8,"""")</f>
+        <v>"Capital"</v>
       </c>
     </row>
-    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="60">
         <v>9</v>
       </c>
-      <c r="B9" s="94" t="s">
-        <v>746</v>
+      <c r="B9" s="95" t="s">
+        <v>758</v>
       </c>
       <c r="C9" s="54" t="s">
         <v>631</v>
@@ -44719,23 +44653,23 @@
       <c r="E9" s="63" t="s">
         <v>740</v>
       </c>
-      <c r="F9" s="67" t="s">
-        <v>762</v>
-      </c>
-      <c r="G9" s="68" t="s">
-        <v>758</v>
-      </c>
-      <c r="H9" s="67" t="s">
-        <v>762</v>
-      </c>
-      <c r="I9" s="63" t="s">
-        <v>742</v>
-      </c>
-      <c r="J9" s="67" t="s">
-        <v>743</v>
-      </c>
-      <c r="K9" s="68" t="s">
-        <v>748</v>
+      <c r="F9" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>1</v>
       </c>
       <c r="L9" s="19" t="s">
         <v>1</v>
@@ -44873,43 +44807,43 @@
         <v>1461</v>
       </c>
       <c r="BE9" s="62" t="str">
-        <f>_xlfn.CONCAT("""",C9,"""")</f>
+        <f t="shared" si="0"/>
         <v>"UF"</v>
       </c>
     </row>
-    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:57" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="60">
         <v>10</v>
       </c>
-      <c r="B10" s="95" t="s">
-        <v>745</v>
+      <c r="B10" s="94" t="s">
+        <v>746</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>635</v>
-      </c>
-      <c r="D10" s="67" t="s">
+        <v>631</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>737</v>
       </c>
-      <c r="E10" s="68" t="s">
-        <v>746</v>
+      <c r="E10" s="63" t="s">
+        <v>740</v>
       </c>
       <c r="F10" s="67" t="s">
-        <v>737</v>
+        <v>762</v>
       </c>
       <c r="G10" s="68" t="s">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="H10" s="67" t="s">
+        <v>762</v>
+      </c>
+      <c r="I10" s="63" t="s">
+        <v>742</v>
+      </c>
+      <c r="J10" s="67" t="s">
         <v>743</v>
       </c>
-      <c r="I10" s="68" t="s">
+      <c r="K10" s="68" t="s">
         <v>748</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>744</v>
-      </c>
-      <c r="K10" s="63" t="s">
-        <v>742</v>
       </c>
       <c r="L10" s="19" t="s">
         <v>1</v>
@@ -44920,9 +44854,8 @@
       <c r="N10" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="O10" s="29" t="str">
-        <f>_xlfn.CONCAT("""É a cidade capital do Estado de ",K10," do Brasil """)</f>
-        <v>"É a cidade capital do Estado de Minas.Gerais do Brasil "</v>
+      <c r="O10" s="40" t="s">
+        <v>1477</v>
       </c>
       <c r="P10" s="61" t="s">
         <v>1</v>
@@ -44931,22 +44864,22 @@
         <v>1</v>
       </c>
       <c r="R10" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="66" t="s">
-        <v>1</v>
+        <v>755</v>
+      </c>
+      <c r="S10" s="69" t="s">
+        <v>759</v>
       </c>
       <c r="T10" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="U10" s="40" t="s">
-        <v>1</v>
+        <v>756</v>
+      </c>
+      <c r="U10" s="64" t="s">
+        <v>760</v>
       </c>
       <c r="V10" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="W10" s="40" t="s">
-        <v>1</v>
+        <v>757</v>
+      </c>
+      <c r="W10" s="29" t="s">
+        <v>761</v>
       </c>
       <c r="X10" s="61" t="s">
         <v>1</v>
@@ -45021,22 +44954,22 @@
         <v>1</v>
       </c>
       <c r="AV10" s="46" t="s">
-        <v>1473</v>
+        <v>1</v>
       </c>
       <c r="AW10" s="62" t="s">
-        <v>1474</v>
+        <v>1</v>
       </c>
       <c r="AX10" s="46" t="s">
         <v>1333</v>
       </c>
       <c r="AY10" s="62" t="s">
-        <v>1475</v>
+        <v>1464</v>
       </c>
       <c r="AZ10" s="46" t="s">
         <v>764</v>
       </c>
       <c r="BA10" s="62" t="s">
-        <v>1476</v>
+        <v>1464</v>
       </c>
       <c r="BB10" s="46" t="s">
         <v>1460</v>
@@ -45048,56 +44981,28 @@
         <v>1461</v>
       </c>
       <c r="BE10" s="62" t="str">
-        <f>_xlfn.CONCAT("""",C10,"""")</f>
-        <v>"Capital"</v>
+        <f t="shared" si="0"/>
+        <v>"UF"</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="F1:F6" xr:uid="{CEF52033-0BF0-4BCC-B911-A6BC1CA10036}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A11:B1048576 D1:F6 H1:XFD6 G2 G4:G5 A1:B2 B3:B6 A3:A10">
-    <cfRule type="cellIs" dxfId="0" priority="49" operator="equal">
+  <conditionalFormatting sqref="A1:A1048576 G2 G4:G5 D10:F1048576 H10:XFD1048576">
+    <cfRule type="cellIs" dxfId="3" priority="52" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8 D8:XFD8">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:F8 H1:XFD8">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10 D9:F1048576 H9:XFD1048576">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B1048576 B1:B6">
-    <cfRule type="duplicateValues" dxfId="7" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:I7">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7:F7 J7:XFD7">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="2" priority="1660"/>
-    <cfRule type="cellIs" dxfId="1" priority="1661" operator="equal">
+  <conditionalFormatting sqref="D9:XFD9">
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
